--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Capital Salud.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Capital Salud.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="G5InHTSA/CzzBkaZEwgrx2ody54JNHPpiR7t1Mjgl2I="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Zj1osQxIPbN5r61eIFxxcHmZO7exATtXHztY6cja210="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>Entidad</t>
   </si>
@@ -80,7 +80,7 @@
  plataforma estratégica de la entidad.</t>
   </si>
   <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Acta No. 123 Aprobación PEI 2021-2024.pdf</t>
+    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Plan Estratégico 2021-2024 DR01-PE.pdf</t>
   </si>
   <si>
     <t>Jerarquía del instrumento</t>
@@ -105,12 +105,6 @@
   </si>
   <si>
     <t>La planeación estratégica representa nuestra hoja de ruta para enfrentar los retos actuales del sector salud, consolidar nuestra posición en el mercado y sobre todo, continuar trabajando para brindar servicios de calidad, accesibles y humanizados a todos nuestro asegurados; este plan fue construido a partir de la vigencia 2024</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/NOTA INTERNA APROBACIÓN POA 2025 FINAL.pdf</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Plan Estratégico 2021-2024 DR01-PE.pdf</t>
   </si>
   <si>
     <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Plan Estatregico 2025-2028 DO-001-DES.pdf</t>
@@ -600,90 +594,8 @@
       </c>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P4" s="4"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P5" s="4"/>
-    </row>
+    <row r="4" ht="14.25" customHeight="1"/>
+    <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1"/>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -1677,8 +1589,6 @@
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
